--- a/VocabEase_admin/src/main/resources/template/template_question.xlsx
+++ b/VocabEase_admin/src/main/resources/template/template_question.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>标题</t>
   </si>
@@ -30,42 +30,121 @@
     <t>Baby don't hurt me! No more!</t>
   </si>
   <si>
-    <t>翻译测试</t>
+    <t>问题描述</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题选项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>答案解析</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>难度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>分类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>答案</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>模板说明：
-1.难度 请直接输入难度系数如：1、2、3、4
-2.分类 请输入已存在的分类名称
-3.切勿反复导入同一文件！！！
-4.模板红色部分仅作示例，参照录入前，请删除示例数据行</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>问题描述</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>答案解释</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>难度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>分类</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>音乐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>OK/No Way</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>选项</t>
+1.问题类型 请直接输入问题代码如：0、1、2、3 （0：判断题、1：单选题、2：多选题、3：填空题）
+2.问题选项 判断题不填，选择题一行一个选项 （例如：A、xxx
+                                                                                           B、yyy
+                                                                                           C、zzz）
+3.答案 判断题仅输入”正确“或”错误“，单选仅输入单个字母，多选输入如：A、B、C
+3.难度 请直接输入难度系数如：1、2、3、4
+4.分类 请输入已存在的分类名称
+5.切勿反复导入同一文件！！！
+6.模板红色部分仅作示例，参照录入前，请删除示例数据行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Oh I don't know</t>
+  </si>
+  <si>
+    <t>why you're not fair</t>
+  </si>
+  <si>
+    <t>问题1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>问题1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A、B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A、I give you my love
+B、but you don't care
+C、So what is right</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>and what is wrong</t>
+  </si>
+  <si>
+    <t>gimme a sign</t>
+  </si>
+  <si>
+    <t>uoh oh...</t>
+  </si>
+  <si>
+    <t>A、Oh I don't know
+B、what can I do
+C、what else can I say</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>it's up to you</t>
+  </si>
+  <si>
+    <t>I know we're one</t>
+  </si>
+  <si>
+    <t>just me and ______</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>you</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>just me and you</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -73,7 +152,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -87,6 +166,18 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -109,10 +200,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -394,64 +490,151 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="109.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="150" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>8</v>
       </c>
+      <c r="G2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
